--- a/output/第10期計画_サービス受給者数データの確認.xlsx
+++ b/output/第10期計画_サービス受給者数データの確認.xlsx
@@ -5662,7 +5662,7 @@
     <row r="31" ht="104" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>注1）推計と実績の差は在宅＋0.35％・居住系＋0.14％・施設▲0.36％であり、いずれも1％未満である。算定チェーンは正しく閉じている。注2）認定者数は令和8年3月末の時点、利用率は令和7年度（令和7年4月〜令和8年1月）の平均であり、厳密には時点が異なる。それでも1％未満で一致するのは、認定者数の年内の変動が小さいためである。注3）未利用者は486.5人（24.5％）である。この人数をどう扱うかで見込量が変わる。現在の未利用率を維持すると置くのが自然であるが、第5章の施策により利用率を上げる目標を立てる場合は、見込量にその分を上乗せする必要がある。手順3で発注者のご意向を確認する。注4）本シートの推計は算定式の検証のためのものであり、第2段階の成果物ではない。第2段階は手順1〜7を経て別途作成する。</t>
+          <t>注1）推計と実績の差は在宅＋0.35％・居住系＋0.14％・施設▲0.36％であり、いずれも1％未満である。算定チェーンは正しく閉じている。注2）認定者数は令和8年3月末の時点、利用率は令和7年度（令和7年4月〜令和8年1月）の平均であり、厳密には時点が異なる。それでも1％未満で一致するのは、認定者数の年内の変動が小さいためである。注3）3区分の合計利用率（51.2％＋7.3％＋17.0％＝75.5％）による未利用者は認定者1,984人の24.5％＝486人である。上表のとおり要介護度別の利用率で加重すると488.6人となるが、これは合計利用率の丸めによる差である。この人数をどう扱うかで見込量が変わる。現在の未利用率を維持すると置くのが自然であるが、第5章の施策により利用率を上げる目標を立てる場合は、見込量にその分を上乗せする必要がある。手順3で発注者のご意向を確認する。注4）本シートの推計は算定式の検証のためのものであり、第2段階の成果物ではない。第2段階は手順1〜7を経て別途作成する。</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>認定者1,984人のうち、在宅・居住系・施設のいずれも利用していない者が486.5人（24.5％）いる。</t>
+          <t>認定者1,984人のうち、在宅・居住系・施設のいずれも利用していない者が486人（24.5％）いる。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">

--- a/output/第10期計画_サービス受給者数データの確認.xlsx
+++ b/output/第10期計画_サービス受給者数データの確認.xlsx
@@ -5925,7 +5925,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>現在の未利用率を維持すると置くのが自然である。第5章の施策により利用率を上げる目標を立てる場合は、見込量に上乗せする必要がある。未利用の理由は資料依頼No.7（未利用認定者の内訳）で照会中である。</t>
+          <t>現在の未利用率を維持すると置くのが自然である。第5章の施策により利用率を上げる目標を立てる場合は、見込量に上乗せする必要がある。未利用の理由は資料依頼No.8（未利用認定者の内訳）で照会中である。</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
